--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,330 +890,330 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>4</v>
+      </c>
+      <c r="D15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="14">
-        <v>3</v>
-      </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
+        <v>9</v>
+      </c>
+      <c r="G15" s="14">
         <v>6</v>
       </c>
-      <c r="G15" s="14">
-        <v>5</v>
-      </c>
       <c r="H15" s="15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>16.666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="M15" s="15">
-        <v>16.666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H16" s="15">
-        <v>16.666666666666</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>16.129032258064</v>
+        <v>10.810810810810</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.454545454545</v>
+        <v>-46.753246753246</v>
       </c>
       <c r="M16" s="15">
-        <v>-40</v>
+        <v>-38.805970149253</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.415094339622</v>
+        <v>-87.267080745341</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F17" s="14">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G17" s="14">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H17" s="15">
-        <v>13.333333333333</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I17" s="14">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="J17" s="14">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="K17" s="15">
-        <v>28.409090909090</v>
+        <v>17.272727272727</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.377049180327</v>
+        <v>-9.790209790209</v>
       </c>
       <c r="M17" s="15">
-        <v>44.871794871794</v>
+        <v>44.943820224719</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.115942028985</v>
+        <v>-18.354430379746</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
+        <v>4</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F18" s="14">
+        <v>10</v>
+      </c>
+      <c r="G18" s="14">
+        <v>18</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-44.444444444444</v>
+      </c>
+      <c r="I18" s="14">
         <v>24</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
-      </c>
-      <c r="F18" s="14">
-        <v>12</v>
-      </c>
-      <c r="G18" s="14">
-        <v>19</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-36.842105263157</v>
-      </c>
-      <c r="I18" s="14">
-        <v>18</v>
-      </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.265306122449</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.221556886227</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
         <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>-43.548387096774</v>
+        <v>-46.774193548387</v>
       </c>
       <c r="I19" s="14">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="K19" s="15">
-        <v>-29.333333333333</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="L19" s="15">
-        <v>-47.524752475247</v>
+        <v>-47.107438016528</v>
       </c>
       <c r="M19" s="15">
-        <v>-17.1875</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N19" s="15">
-        <v>-30.263157894736</v>
+        <v>-25.581395348837</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
         <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F20" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>20.833333333333</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="I20" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J20" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>43.75</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.984126984127</v>
+        <v>-28.169014084507</v>
       </c>
       <c r="M20" s="15">
-        <v>70.370370370370</v>
+        <v>50</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.268656716417</v>
+        <v>-87.055837563451</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D21" s="17">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.127659574468</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="G21" s="17">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.717948717948</v>
+        <v>-20.476190476190</v>
       </c>
       <c r="I21" s="17">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="J21" s="17">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="K21" s="18">
-        <v>5</v>
+        <v>1.265822784810</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.090909090909</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.208333333333</v>
+        <v>-1.840490797546</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.727272727272</v>
+        <v>-72.904318374259</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
+        <v>29</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F22" s="14">
-        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
+        <v>22</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-36.363636363636</v>
+      </c>
+      <c r="I23" s="14">
+        <v>27</v>
+      </c>
+      <c r="J23" s="14">
+        <v>29</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-6.896551724137</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-12.903225806451</v>
+      </c>
+      <c r="M23" s="15">
+        <v>35</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>21</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-23.809523809523</v>
-      </c>
-      <c r="I23" s="14">
-        <v>25</v>
-      </c>
-      <c r="J23" s="14">
-        <v>26</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-3.846153846153</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-3.846153846153</v>
-      </c>
-      <c r="M23" s="15">
-        <v>31.578947368421</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>50</v>
+      </c>
+      <c r="D24" s="14">
         <v>44</v>
       </c>
-      <c r="D24" s="14">
-        <v>52</v>
-      </c>
       <c r="E24" s="15">
-        <v>-15.384615384615</v>
+        <v>13.636363636363</v>
       </c>
       <c r="F24" s="14">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G24" s="14">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.104166666666</v>
+        <v>-11.282051282051</v>
       </c>
       <c r="I24" s="14">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="J24" s="14">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.560606060606</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.521739130434</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="M24" s="15">
-        <v>33.540372670807</v>
+        <v>41.935483870967</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1306,37 +1306,37 @@
         <v>16</v>
       </c>
       <c r="D25" s="14">
+        <v>19</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-15.789473684210</v>
+      </c>
+      <c r="F25" s="14">
+        <v>51</v>
+      </c>
+      <c r="G25" s="14">
+        <v>76</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-32.894736842105</v>
+      </c>
+      <c r="I25" s="14">
+        <v>77</v>
+      </c>
+      <c r="J25" s="14">
+        <v>115</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-33.043478260869</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="M25" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="15">
-        <v>-23.809523809523</v>
-      </c>
-      <c r="F25" s="14">
-        <v>45</v>
-      </c>
-      <c r="G25" s="14">
-        <v>70</v>
-      </c>
-      <c r="H25" s="15">
-        <v>-35.714285714285</v>
-      </c>
-      <c r="I25" s="14">
-        <v>61</v>
-      </c>
-      <c r="J25" s="14">
-        <v>96</v>
-      </c>
-      <c r="K25" s="15">
-        <v>-36.458333333333</v>
-      </c>
-      <c r="L25" s="15">
-        <v>-18.666666666666</v>
-      </c>
-      <c r="M25" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
+        <v>24</v>
+      </c>
+      <c r="E26" s="15">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>105</v>
+      </c>
+      <c r="G26" s="14">
+        <v>84</v>
+      </c>
+      <c r="H26" s="15">
+        <v>25</v>
+      </c>
+      <c r="I26" s="14">
+        <v>167</v>
+      </c>
+      <c r="J26" s="14">
+        <v>156</v>
+      </c>
+      <c r="K26" s="15">
+        <v>7.051282051282</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-11.640211640211</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-16.080402010050</v>
+      </c>
+      <c r="N26" s="13" t="s">
         <v>21</v>
-      </c>
-      <c r="E26" s="15">
-        <v>61.904761904761</v>
-      </c>
-      <c r="F26" s="14">
-        <v>108</v>
-      </c>
-      <c r="G26" s="14">
-        <v>99</v>
-      </c>
-      <c r="H26" s="15">
-        <v>9.090909090909</v>
-      </c>
-      <c r="I26" s="14">
-        <v>144</v>
-      </c>
-      <c r="J26" s="14">
-        <v>132</v>
-      </c>
-      <c r="K26" s="15">
-        <v>9.090909090909</v>
-      </c>
-      <c r="L26" s="15">
-        <v>-13.772455089820</v>
-      </c>
-      <c r="M26" s="15">
-        <v>-18.644067796610</v>
-      </c>
-      <c r="N26" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>4</v>
+      </c>
+      <c r="D27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>3</v>
-      </c>
       <c r="E27" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G27" s="14">
         <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-12.5</v>
+        <v>25</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>29</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1479,28 +1479,28 @@
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L29" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
         <v>-55.555555555555</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,28 +1520,28 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L30" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
         <v>-57.142857142857</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.682926829268</v>
+        <v>-93.023255813953</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,13 +1576,13 @@
         <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1635,13 +1635,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>133</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>3452</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>1789</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>2433</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>1286</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>3071</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>12273</v>

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -199,61 +199,61 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -851,714 +851,714 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
+        <v>2</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I14" s="14">
         <v>1</v>
       </c>
-      <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G15" s="14">
         <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>37.5</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L15" s="15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="N15" s="15">
-        <v>37.5</v>
+        <v>55.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H16" s="15">
-        <v>-3.846153846153</v>
+        <v>3.571428571428</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K16" s="15">
-        <v>10.810810810810</v>
+        <v>8.888888888888</v>
       </c>
       <c r="L16" s="15">
-        <v>-46.753246753246</v>
+        <v>-44.318181818181</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.805970149253</v>
+        <v>-31.944444444444</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.267080745341</v>
+        <v>-86.350974930362</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E17" s="15">
-        <v>-45.454545454545</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="F17" s="14">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17" s="14">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.695652173913</v>
+        <v>-23.75</v>
       </c>
       <c r="I17" s="14">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="J17" s="14">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="K17" s="15">
-        <v>17.272727272727</v>
+        <v>4.347826086956</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.790209790209</v>
+        <v>-8.280254777070</v>
       </c>
       <c r="M17" s="15">
-        <v>44.943820224719</v>
+        <v>37.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.354430379746</v>
+        <v>-21.739130434782</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-44.444444444444</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.580645161290</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.580645161290</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.846153846153</v>
+        <v>-54.385964912280</v>
       </c>
       <c r="N18" s="15">
-        <v>-88</v>
+        <v>-88.495575221238</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G19" s="14">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>-46.774193548387</v>
+        <v>-39.344262295082</v>
       </c>
       <c r="I19" s="14">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="J19" s="14">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="K19" s="15">
-        <v>-28.888888888888</v>
+        <v>-28.971962616822</v>
       </c>
       <c r="L19" s="15">
-        <v>-47.107438016528</v>
+        <v>-43.703703703703</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.111111111111</v>
+        <v>-8.433734939759</v>
       </c>
       <c r="N19" s="15">
-        <v>-25.581395348837</v>
+        <v>-22.448979591836</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-14.285714285714</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F20" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
         <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>-3.571428571428</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="I20" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J20" s="14">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="K20" s="15">
-        <v>30.769230769230</v>
+        <v>14.583333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.169014084507</v>
+        <v>-32.098765432098</v>
       </c>
       <c r="M20" s="15">
-        <v>50</v>
+        <v>48.648648648648</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.055837563451</v>
+        <v>-87.695749440715</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E21" s="18">
-        <v>-28.571428571428</v>
+        <v>-36.764705882352</v>
       </c>
       <c r="F21" s="17">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G21" s="17">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.476190476190</v>
+        <v>-20.642201834862</v>
       </c>
       <c r="I21" s="17">
-        <v>320</v>
+        <v>365</v>
       </c>
       <c r="J21" s="17">
-        <v>316</v>
+        <v>384</v>
       </c>
       <c r="K21" s="18">
-        <v>1.265822784810</v>
+        <v>-4.947916666666</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.888888888888</v>
+        <v>-27.722772277227</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.840490797546</v>
+        <v>-0.273224043715</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.904318374259</v>
+        <v>-72.700074794315</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
+      </c>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-44.444444444444</v>
+        <v>-30</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="F23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>-36.363636363636</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I23" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J23" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.896551724137</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.903225806451</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="M23" s="15">
-        <v>35</v>
+        <v>52.380952380952</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E24" s="15">
-        <v>13.636363636363</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="F24" s="14">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="G24" s="14">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.282051282051</v>
+        <v>-15.706806282722</v>
       </c>
       <c r="I24" s="14">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="J24" s="14">
-        <v>308</v>
+        <v>359</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.285714285714</v>
+        <v>-15.598885793871</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.714285714285</v>
+        <v>-4.416403785488</v>
       </c>
       <c r="M24" s="15">
-        <v>41.935483870967</v>
+        <v>40.277777777777</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E25" s="15">
-        <v>-15.789473684210</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="F25" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G25" s="14">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.894736842105</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J25" s="14">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.043478260869</v>
+        <v>-35.915492957746</v>
       </c>
       <c r="L25" s="15">
         <v>-22.222222222222</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="G26" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H26" s="15">
-        <v>25</v>
+        <v>31.868131868131</v>
       </c>
       <c r="I26" s="14">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="J26" s="14">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="K26" s="15">
-        <v>7.051282051282</v>
+        <v>10.928961748633</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.640211640211</v>
+        <v>-4.694835680751</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.080402010050</v>
+        <v>-11.353711790393</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
         <v>4</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F27" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>25</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L27" s="15">
-        <v>-7.692307692307</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
+        <v>700</v>
+      </c>
+      <c r="F28" s="14">
+        <v>14</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="15">
+        <v>133.333333333333</v>
+      </c>
+      <c r="I28" s="14">
+        <v>18</v>
+      </c>
+      <c r="J28" s="14">
+        <v>12</v>
+      </c>
+      <c r="K28" s="15">
         <v>50</v>
       </c>
-      <c r="F28" s="14">
-        <v>8</v>
-      </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
-      <c r="H28" s="15">
-        <v>60</v>
-      </c>
-      <c r="I28" s="14">
-        <v>12</v>
-      </c>
-      <c r="J28" s="14">
-        <v>11</v>
-      </c>
-      <c r="K28" s="15">
-        <v>9.090909090909</v>
-      </c>
       <c r="L28" s="15">
-        <v>9.090909090909</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+        <v>35</v>
+      </c>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>4</v>
       </c>
       <c r="H29" s="15">
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
+        <v>6</v>
+      </c>
+      <c r="J29" s="14">
+        <v>10</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-40</v>
+      </c>
+      <c r="L29" s="15">
         <v>-50</v>
       </c>
-      <c r="I29" s="14">
-        <v>4</v>
-      </c>
-      <c r="J29" s="14">
-        <v>9</v>
-      </c>
-      <c r="K29" s="15">
-        <v>-55.555555555555</v>
-      </c>
-      <c r="L29" s="15">
-        <v>-60</v>
-      </c>
       <c r="M29" s="15">
-        <v>-55.555555555555</v>
+        <v>-40</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.304347826087</v>
+        <v>-88.679245283018</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
-        <v>-66.666666666666</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M30" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.023255813953</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="D31" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
@@ -1567,7 +1567,7 @@
         <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
@@ -1576,13 +1576,13 @@
         <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,16 +1608,16 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>38</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
@@ -1629,19 +1629,19 @@
         <v>1</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>133</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>3452</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>1789</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>2433</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>1286</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>3071</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>12273</v>

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,12 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
     <t>Transit</t>
   </si>
   <si>
-    <t>***.*</t>
-  </si>
-  <si>
     <t>Housing</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -851,14 +851,14 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>0</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -885,689 +885,689 @@
         <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.857142857142</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>10</v>
+      </c>
+      <c r="G15" s="14">
+        <v>8</v>
+      </c>
+      <c r="H15" s="15">
+        <v>25</v>
+      </c>
+      <c r="I15" s="14">
+        <v>15</v>
+      </c>
+      <c r="J15" s="14">
         <v>11</v>
       </c>
-      <c r="G15" s="14">
-        <v>6</v>
-      </c>
-      <c r="H15" s="15">
-        <v>83.333333333333</v>
-      </c>
-      <c r="I15" s="14">
-        <v>14</v>
-      </c>
-      <c r="J15" s="14">
-        <v>9</v>
-      </c>
       <c r="K15" s="15">
-        <v>55.555555555555</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>114.285714285714</v>
       </c>
       <c r="M15" s="15">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="N15" s="15">
-        <v>55.555555555555</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H16" s="15">
-        <v>3.571428571428</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J16" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K16" s="15">
-        <v>8.888888888888</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.318181818181</v>
+        <v>-49.056603773584</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.944444444444</v>
+        <v>-40.659340659340</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.350974930362</v>
+        <v>-86.987951807228</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E17" s="15">
-        <v>-46.428571428571</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F17" s="14">
         <v>61</v>
       </c>
       <c r="G17" s="14">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.75</v>
+        <v>-33.695652173913</v>
       </c>
       <c r="I17" s="14">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="J17" s="14">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="K17" s="15">
-        <v>4.347826086956</v>
+        <v>-1.234567901234</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.280254777070</v>
+        <v>-10.614525139664</v>
       </c>
       <c r="M17" s="15">
-        <v>37.142857142857</v>
+        <v>41.592920353982</v>
       </c>
       <c r="N17" s="15">
-        <v>-21.739130434782</v>
+        <v>-24.528301886792</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-15.384615384615</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-25.714285714285</v>
+        <v>-27.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.529411764705</v>
+        <v>-27.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.385964912280</v>
+        <v>-56.060606060606</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.495575221238</v>
+        <v>-88.627450980392</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-29.411764705882</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H19" s="15">
-        <v>-39.344262295082</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="I19" s="14">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="K19" s="15">
-        <v>-28.971962616822</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="L19" s="15">
-        <v>-43.703703703703</v>
+        <v>-41.509433962264</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.433734939759</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="N19" s="15">
-        <v>-22.448979591836</v>
+        <v>-21.848739495798</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>-55.555555555555</v>
+        <v>-40</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H20" s="15">
-        <v>-17.857142857142</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I20" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J20" s="14">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K20" s="15">
-        <v>14.583333333333</v>
+        <v>6.896551724137</v>
       </c>
       <c r="L20" s="15">
-        <v>-32.098765432098</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="M20" s="15">
-        <v>48.648648648648</v>
+        <v>51.219512195122</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.695749440715</v>
+        <v>-87.914230019493</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
         <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.764705882352</v>
+        <v>-31.746031746031</v>
       </c>
       <c r="F21" s="17">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G21" s="17">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.642201834862</v>
+        <v>-23.504273504273</v>
       </c>
       <c r="I21" s="17">
-        <v>365</v>
+        <v>414</v>
       </c>
       <c r="J21" s="17">
-        <v>384</v>
+        <v>447</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.947916666666</v>
+        <v>-7.382550335570</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.722772277227</v>
+        <v>-29.351535836177</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.273224043715</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.700074794315</v>
+        <v>-73.169151004536</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
         <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L22" s="15">
-        <v>133.333333333333</v>
+        <v>125</v>
       </c>
       <c r="M22" s="15">
-        <v>-30</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E23" s="15">
-        <v>-20</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F23" s="14">
         <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H23" s="15">
-        <v>-11.764705882352</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="I23" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J23" s="14">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K23" s="15">
-        <v>-5.882352941176</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="L23" s="15">
-        <v>-13.513513513513</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="M23" s="15">
-        <v>52.380952380952</v>
+        <v>42.307692307692</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E24" s="15">
-        <v>-21.568627450980</v>
+        <v>-27.118644067796</v>
       </c>
       <c r="F24" s="14">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="G24" s="14">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.706806282722</v>
+        <v>-13.592233009708</v>
       </c>
       <c r="I24" s="14">
-        <v>303</v>
+        <v>348</v>
       </c>
       <c r="J24" s="14">
-        <v>359</v>
+        <v>418</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.598885793871</v>
+        <v>-16.746411483253</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.416403785488</v>
+        <v>-4.657534246575</v>
       </c>
       <c r="M24" s="15">
-        <v>40.277777777777</v>
+        <v>46.835443037974</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>-48.148148148148</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G25" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.714285714285</v>
+        <v>-35.164835164835</v>
       </c>
       <c r="I25" s="14">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J25" s="14">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.915492957746</v>
+        <v>-37.349397590361</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.222222222222</v>
+        <v>-26.241134751773</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F26" s="14">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="G26" s="14">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H26" s="15">
-        <v>31.868131868131</v>
+        <v>15.306122448979</v>
       </c>
       <c r="I26" s="14">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="J26" s="14">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="K26" s="15">
-        <v>10.928961748633</v>
+        <v>6.220095693779</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.694835680751</v>
+        <v>-9.387755102040</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.353711790393</v>
+        <v>-14.615384615384</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>300</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
-        <v>85.714285714285</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>30.769230769230</v>
+        <v>12.5</v>
       </c>
       <c r="L27" s="15">
-        <v>13.333333333333</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>133.333333333333</v>
+        <v>250</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>46.153846153846</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
         <v>2</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I29" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J29" s="14">
         <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.679245283018</v>
+        <v>-87.301587301587</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
+        <v>2</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
+        <v>3</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="15">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
-        <v>2</v>
-      </c>
-      <c r="G30" s="14">
-        <v>4</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-50</v>
-      </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J30" s="14">
         <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L30" s="15">
-        <v>-63.636363636363</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-92</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+        <v>20</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
@@ -1575,14 +1575,14 @@
       <c r="K31" s="15">
         <v>-100</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>28</v>
+      <c r="L31" s="15">
+        <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,7 +1608,7 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D33" s="14">
         <v>1</v>
@@ -1617,10 +1617,10 @@
         <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1629,19 +1629,19 @@
         <v>1</v>
       </c>
       <c r="J33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>133</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>3452</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>1789</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>2433</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>1286</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>3071</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>12273</v>

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -864,10 +864,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -885,48 +885,48 @@
         <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>36.363636363636</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>114.285714285714</v>
+        <v>77.777777777777</v>
       </c>
       <c r="M15" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>25</v>
+        <v>6.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F16" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>3.846153846153</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J16" s="14">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>5.882352941176</v>
+        <v>-4.6875</v>
       </c>
       <c r="L16" s="15">
-        <v>-49.056603773584</v>
+        <v>-49.166666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.659340659340</v>
+        <v>-41.904761904761</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.987951807228</v>
+        <v>-87.370600414078</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D17" s="14">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-45.833333333333</v>
+        <v>53.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G17" s="14">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H17" s="15">
-        <v>-33.695652173913</v>
+        <v>-22.471910112359</v>
       </c>
       <c r="I17" s="14">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="J17" s="14">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.234567901234</v>
+        <v>5.649717514124</v>
       </c>
       <c r="L17" s="15">
-        <v>-10.614525139664</v>
+        <v>-4.102564102564</v>
       </c>
       <c r="M17" s="15">
-        <v>41.592920353982</v>
+        <v>48.412698412698</v>
       </c>
       <c r="N17" s="15">
-        <v>-24.528301886792</v>
+        <v>-21.097046413502</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
         <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.060606060606</v>
+        <v>-57.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.627450980392</v>
+        <v>-88.927335640138</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H19" s="15">
-        <v>-20.689655172413</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="J19" s="14">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.390243902439</v>
+        <v>-18.840579710144</v>
       </c>
       <c r="L19" s="15">
-        <v>-41.509433962264</v>
+        <v>-35.632183908046</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.060606060606</v>
+        <v>5.660377358490</v>
       </c>
       <c r="N19" s="15">
-        <v>-21.848739495798</v>
+        <v>-15.151515151515</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-40</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H20" s="15">
-        <v>-27.272727272727</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J20" s="14">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="K20" s="15">
-        <v>6.896551724137</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-32.608695652173</v>
+        <v>-34.313725490196</v>
       </c>
       <c r="M20" s="15">
-        <v>51.219512195122</v>
+        <v>48.888888888888</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.914230019493</v>
+        <v>-88.388214904679</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D21" s="17">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E21" s="18">
-        <v>-31.746031746031</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="F21" s="17">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="G21" s="17">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.504273504273</v>
+        <v>-21.311475409836</v>
       </c>
       <c r="I21" s="17">
-        <v>414</v>
+        <v>476</v>
       </c>
       <c r="J21" s="17">
-        <v>447</v>
+        <v>504</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.382550335570</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.351535836177</v>
+        <v>-26.429675425038</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.816901408450</v>
+        <v>0.634249471458</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.169151004536</v>
+        <v>-72.831050228310</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>66.666666666666</v>
+        <v>150</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>28.571428571428</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="M22" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>5</v>
       </c>
       <c r="D23" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-58.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G23" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H23" s="15">
-        <v>-46.428571428571</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="I23" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J23" s="14">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K23" s="15">
-        <v>-19.565217391304</v>
+        <v>-18.867924528301</v>
       </c>
       <c r="L23" s="15">
-        <v>-9.756097560975</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="M23" s="15">
-        <v>42.307692307692</v>
+        <v>53.571428571428</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D24" s="14">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E24" s="15">
-        <v>-27.118644067796</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="G24" s="14">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.592233009708</v>
+        <v>-4.455445544554</v>
       </c>
       <c r="I24" s="14">
-        <v>348</v>
+        <v>404</v>
       </c>
       <c r="J24" s="14">
-        <v>418</v>
+        <v>466</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.746411483253</v>
+        <v>-13.304721030042</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.657534246575</v>
+        <v>-1.463414634146</v>
       </c>
       <c r="M24" s="15">
-        <v>46.835443037974</v>
+        <v>49.077490774907</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.833333333333</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F25" s="14">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G25" s="14">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.164835164835</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I25" s="14">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="J25" s="14">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="K25" s="15">
-        <v>-37.349397590361</v>
+        <v>-36.413043478260</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.241134751773</v>
+        <v>-26.415094339622</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.384615384615</v>
+        <v>3.703703703703</v>
       </c>
       <c r="F26" s="14">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G26" s="14">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H26" s="15">
-        <v>15.306122448979</v>
+        <v>-0.961538461538</v>
       </c>
       <c r="I26" s="14">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="J26" s="14">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="K26" s="15">
-        <v>6.220095693779</v>
+        <v>4.237288135593</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.387755102040</v>
+        <v>-11.191335740072</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.615384615384</v>
+        <v>-16.891891891891</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>12</v>
       </c>
       <c r="G27" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I27" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>12.5</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L27" s="15">
-        <v>20</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
         <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>46.153846153846</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>35.714285714285</v>
+        <v>37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,10 +1479,10 @@
         <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
         <v>8</v>
@@ -1497,18 +1497,18 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N29" s="15">
-        <v>-87.301587301587</v>
+        <v>-88.405797101449</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>2</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1520,10 +1520,10 @@
         <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
         <v>6</v>
@@ -1538,10 +1538,10 @@
         <v>-45.454545454545</v>
       </c>
       <c r="M30" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,72 +861,72 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L14" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M14" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="M14" s="15">
-        <v>-75</v>
-      </c>
       <c r="N14" s="15">
-        <v>-94.736842105263</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
+        <v>20</v>
+      </c>
+      <c r="I15" s="14">
+        <v>18</v>
+      </c>
+      <c r="J15" s="14">
+        <v>13</v>
+      </c>
+      <c r="K15" s="15">
+        <v>38.461538461538</v>
+      </c>
+      <c r="L15" s="15">
+        <v>38.461538461538</v>
+      </c>
+      <c r="M15" s="15">
         <v>50</v>
       </c>
-      <c r="I15" s="14">
-        <v>16</v>
-      </c>
-      <c r="J15" s="14">
-        <v>12</v>
-      </c>
-      <c r="K15" s="15">
-        <v>33.333333333333</v>
-      </c>
-      <c r="L15" s="15">
-        <v>77.777777777777</v>
-      </c>
-      <c r="M15" s="15">
-        <v>33.333333333333</v>
-      </c>
       <c r="N15" s="15">
-        <v>6.666666666666</v>
+        <v>5.882352941176</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-46.153846153846</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H16" s="15">
-        <v>-27.272727272727</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J16" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.6875</v>
+        <v>-8.219178082191</v>
       </c>
       <c r="L16" s="15">
-        <v>-49.166666666666</v>
+        <v>-48.461538461538</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.904761904761</v>
+        <v>-44.166666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.370600414078</v>
+        <v>-87.773722627737</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>53.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G17" s="14">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.471910112359</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="J17" s="14">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="K17" s="15">
-        <v>5.649717514124</v>
+        <v>7.216494845360</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.102564102564</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="M17" s="15">
-        <v>48.412698412698</v>
+        <v>50.724637681159</v>
       </c>
       <c r="N17" s="15">
-        <v>-21.097046413502</v>
+        <v>-20.912547528517</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-41.176470588235</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="I18" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.272727272727</v>
+        <v>-34</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.272727272727</v>
+        <v>-32.653061224489</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.333333333333</v>
+        <v>-59.756097560975</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.927335640138</v>
+        <v>-89.751552795031</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-6.666666666666</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G19" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.523809523809</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I19" s="14">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="J19" s="14">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.840579710144</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="L19" s="15">
-        <v>-35.632183908046</v>
+        <v>-30.481283422459</v>
       </c>
       <c r="M19" s="15">
-        <v>5.660377358490</v>
+        <v>3.174603174603</v>
       </c>
       <c r="N19" s="15">
-        <v>-15.151515151515</v>
+        <v>-13.907284768211</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H20" s="15">
-        <v>-37.142857142857</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="I20" s="14">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="J20" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-3.896103896103</v>
       </c>
       <c r="L20" s="15">
-        <v>-34.313725490196</v>
+        <v>-32.727272727272</v>
       </c>
       <c r="M20" s="15">
-        <v>48.888888888888</v>
+        <v>57.446808510638</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.388214904679</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.280701754386</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G21" s="17">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.311475409836</v>
+        <v>-20.161290322580</v>
       </c>
       <c r="I21" s="17">
-        <v>476</v>
+        <v>532</v>
       </c>
       <c r="J21" s="17">
-        <v>504</v>
+        <v>564</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.555555555555</v>
+        <v>-5.673758865248</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.429675425038</v>
+        <v>-24.858757062146</v>
       </c>
       <c r="M21" s="18">
-        <v>0.634249471458</v>
+        <v>0.188323917137</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.831050228310</v>
+        <v>-72.717948717948</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>150</v>
       </c>
       <c r="M22" s="15">
-        <v>-9.090909090909</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-28.571428571428</v>
+        <v>300</v>
       </c>
       <c r="F23" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G23" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H23" s="15">
-        <v>-37.037037037037</v>
+        <v>-24</v>
       </c>
       <c r="I23" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J23" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K23" s="15">
-        <v>-18.867924528301</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="L23" s="15">
-        <v>-6.521739130434</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>53.571428571428</v>
+        <v>61.290322580645</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>52</v>
       </c>
       <c r="D24" s="14">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E24" s="15">
-        <v>8.333333333333</v>
+        <v>26.829268292682</v>
       </c>
       <c r="F24" s="14">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G24" s="14">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.455445544554</v>
+        <v>-2.010050251256</v>
       </c>
       <c r="I24" s="14">
-        <v>404</v>
+        <v>455</v>
       </c>
       <c r="J24" s="14">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.304721030042</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.463414634146</v>
+        <v>0.886917960088</v>
       </c>
       <c r="M24" s="15">
-        <v>49.077490774907</v>
+        <v>52.173913043478</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-38.888888888888</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" s="14">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.363636363636</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I25" s="14">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="J25" s="14">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K25" s="15">
-        <v>-36.413043478260</v>
+        <v>-32.663316582914</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.415094339622</v>
+        <v>-22.988505747126</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>28</v>
       </c>
       <c r="D26" s="14">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E26" s="15">
-        <v>3.703703703703</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="14">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G26" s="14">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="H26" s="15">
-        <v>-0.961538461538</v>
+        <v>-6.956521739130</v>
       </c>
       <c r="I26" s="14">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="J26" s="14">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="K26" s="15">
-        <v>4.237288135593</v>
+        <v>-0.369003690036</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.191335740072</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.891891891891</v>
+        <v>-19.402985074626</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
+        <v>100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>10</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="I27" s="14">
+        <v>23</v>
+      </c>
+      <c r="J27" s="14">
+        <v>18</v>
+      </c>
+      <c r="K27" s="15">
+        <v>27.777777777777</v>
+      </c>
+      <c r="L27" s="15">
         <v>0</v>
-      </c>
-      <c r="F27" s="14">
-        <v>12</v>
-      </c>
-      <c r="G27" s="14">
-        <v>7</v>
-      </c>
-      <c r="H27" s="15">
-        <v>71.428571428571</v>
-      </c>
-      <c r="I27" s="14">
-        <v>20</v>
-      </c>
-      <c r="J27" s="14">
-        <v>17</v>
-      </c>
-      <c r="K27" s="15">
-        <v>17.647058823529</v>
-      </c>
-      <c r="L27" s="15">
-        <v>5.263157894736</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F28" s="14">
         <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="I28" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>57.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,39 +1476,39 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="I29" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29" s="14">
         <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-27.272727272727</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.405797101449</v>
+        <v>-86.486486486486</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>2</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="I30" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J30" s="14">
         <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-45.454545454545</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M30" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.909090909090</v>
+        <v>-88.571428571428</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,13 +861,13 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
-      </c>
-      <c r="G14" s="14">
         <v>1</v>
       </c>
-      <c r="H14" s="15">
-        <v>100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -885,7 +885,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-90</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
         <v>6</v>
       </c>
-      <c r="G15" s="14">
-        <v>5</v>
-      </c>
       <c r="H15" s="15">
-        <v>20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>38.461538461538</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>38.461538461538</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>35.714285714285</v>
       </c>
       <c r="N15" s="15">
-        <v>5.882352941176</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H16" s="15">
-        <v>-30.555555555555</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="I16" s="14">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J16" s="14">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.219178082191</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-48.461538461538</v>
+        <v>-48.201438848920</v>
       </c>
       <c r="M16" s="15">
-        <v>-44.166666666666</v>
+        <v>-45.864661654135</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.773722627737</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
         <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G17" s="14">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.714285714285</v>
+        <v>1.315789473684</v>
       </c>
       <c r="I17" s="14">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="J17" s="14">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="K17" s="15">
-        <v>7.216494845360</v>
+        <v>6.542056074766</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.703703703703</v>
+        <v>-2.978723404255</v>
       </c>
       <c r="M17" s="15">
-        <v>50.724637681159</v>
+        <v>48.051948051948</v>
       </c>
       <c r="N17" s="15">
-        <v>-20.912547528517</v>
+        <v>-21.379310344827</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-83.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-63.157894736842</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K18" s="15">
-        <v>-34</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="L18" s="15">
-        <v>-32.653061224489</v>
+        <v>-34.545454545454</v>
       </c>
       <c r="M18" s="15">
-        <v>-59.756097560975</v>
+        <v>-60</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.751552795031</v>
+        <v>-90.136986301369</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E19" s="15">
-        <v>-17.647058823529</v>
+        <v>-32</v>
       </c>
       <c r="F19" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.692307692307</v>
+        <v>-13.698630136986</v>
       </c>
       <c r="I19" s="14">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="J19" s="14">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.129032258064</v>
+        <v>-18.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-30.481283422459</v>
+        <v>-29.326923076923</v>
       </c>
       <c r="M19" s="15">
-        <v>3.174603174603</v>
+        <v>0.684931506849</v>
       </c>
       <c r="N19" s="15">
-        <v>-13.907284768211</v>
+        <v>-10.909090909090</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H20" s="15">
-        <v>-39.473684210526</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="I20" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J20" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.896103896103</v>
+        <v>-3.658536585365</v>
       </c>
       <c r="L20" s="15">
-        <v>-32.727272727272</v>
+        <v>-32.478632478632</v>
       </c>
       <c r="M20" s="15">
-        <v>57.446808510638</v>
+        <v>54.901960784313</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.235294117647</v>
+        <v>-88.313609467455</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D21" s="17">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="F21" s="17">
         <v>198</v>
       </c>
       <c r="G21" s="17">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.161290322580</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="I21" s="17">
-        <v>532</v>
+        <v>583</v>
       </c>
       <c r="J21" s="17">
-        <v>564</v>
+        <v>630</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.673758865248</v>
+        <v>-7.460317460317</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.858757062146</v>
+        <v>-24.383916990920</v>
       </c>
       <c r="M21" s="18">
-        <v>0.188323917137</v>
+        <v>-1.851851851851</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.717948717948</v>
+        <v>-72.757009345794</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
@@ -1210,7 +1210,7 @@
         <v>150</v>
       </c>
       <c r="M22" s="15">
-        <v>-16.666666666666</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" s="14">
         <v>25</v>
       </c>
       <c r="H23" s="15">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J23" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K23" s="15">
-        <v>-7.407407407407</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="L23" s="15">
-        <v>4.166666666666</v>
+        <v>3.773584905660</v>
       </c>
       <c r="M23" s="15">
-        <v>61.290322580645</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D24" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E24" s="15">
-        <v>26.829268292682</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F24" s="14">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="G24" s="14">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.010050251256</v>
+        <v>9.473684210526</v>
       </c>
       <c r="I24" s="14">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="J24" s="14">
-        <v>507</v>
+        <v>549</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.256410256410</v>
+        <v>-6.557377049180</v>
       </c>
       <c r="L24" s="15">
-        <v>0.886917960088</v>
+        <v>1.785714285714</v>
       </c>
       <c r="M24" s="15">
-        <v>52.173913043478</v>
+        <v>54.054054054054</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E25" s="15">
         <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G25" s="14">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.142857142857</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="I25" s="14">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="J25" s="14">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.663316582914</v>
+        <v>-29.545454545454</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.988505747126</v>
+        <v>-22.5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D26" s="14">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>-20</v>
+        <v>4</v>
       </c>
       <c r="F26" s="14">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G26" s="14">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.956521739130</v>
+        <v>-12.389380530973</v>
       </c>
       <c r="I26" s="14">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="J26" s="14">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.369003690036</v>
+        <v>1.013513513513</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.764705882352</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.402985074626</v>
+        <v>-18.970189701897</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F27" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K27" s="15">
-        <v>27.777777777777</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,31 +1426,31 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>-57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
+        <v>12</v>
+      </c>
+      <c r="G28" s="14">
         <v>14</v>
       </c>
-      <c r="G28" s="14">
-        <v>10</v>
-      </c>
       <c r="H28" s="15">
-        <v>40</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>14.285714285714</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L28" s="15">
         <v>33.333333333333</v>
@@ -1467,7 +1467,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>6</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>500</v>
+        <v>5</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J29" s="14">
         <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L29" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M29" s="15">
-        <v>-28.571428571428</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.486486486486</v>
+        <v>-86.585365853658</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,7 +1508,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,29 +1519,29 @@
       <c r="F30" s="14">
         <v>5</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>400</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J30" s="14">
         <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L30" s="15">
-        <v>-27.272727272727</v>
+        <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.571428571428</v>
+        <v>-88.461538461538</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1620,7 +1620,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -879,36 +879,36 @@
         <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.592592592592</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="15">
         <v>-50</v>
-      </c>
-      <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>6</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>19</v>
@@ -923,10 +923,10 @@
         <v>35.714285714285</v>
       </c>
       <c r="M15" s="15">
-        <v>35.714285714285</v>
+        <v>11.764705882352</v>
       </c>
       <c r="N15" s="15">
-        <v>-5</v>
+        <v>-13.636363636363</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E16" s="15">
-        <v>-54.545454545454</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H16" s="15">
-        <v>-43.589743589743</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="I16" s="14">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J16" s="14">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.285714285714</v>
+        <v>-17.525773195876</v>
       </c>
       <c r="L16" s="15">
-        <v>-48.201438848920</v>
+        <v>-48.717948717948</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.864661654135</v>
+        <v>-45.945945945945</v>
       </c>
       <c r="N16" s="15">
-        <v>-88</v>
+        <v>-88.095238095238</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>4.545454545454</v>
       </c>
       <c r="F17" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G17" s="14">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H17" s="15">
-        <v>1.315789473684</v>
+        <v>16.216216216216</v>
       </c>
       <c r="I17" s="14">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="J17" s="14">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="K17" s="15">
-        <v>6.542056074766</v>
+        <v>7.203389830508</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.978723404255</v>
+        <v>-1.937984496124</v>
       </c>
       <c r="M17" s="15">
-        <v>48.051948051948</v>
+        <v>44.571428571428</v>
       </c>
       <c r="N17" s="15">
-        <v>-21.379310344827</v>
+        <v>-21.183800623053</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-55.555555555555</v>
+        <v>-68.75</v>
       </c>
       <c r="I18" s="14">
         <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K18" s="15">
-        <v>-32.075471698113</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>-34.545454545454</v>
+        <v>-40</v>
       </c>
       <c r="M18" s="15">
-        <v>-60</v>
+        <v>-64.356435643564</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.136986301369</v>
+        <v>-91.133004926108</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>-32</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F19" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G19" s="14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.698630136986</v>
+        <v>-15.189873417721</v>
       </c>
       <c r="I19" s="14">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="J19" s="14">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.333333333333</v>
+        <v>-17.821782178217</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.326923076923</v>
+        <v>-27.510917030567</v>
       </c>
       <c r="M19" s="15">
-        <v>0.684931506849</v>
+        <v>6.410256410256</v>
       </c>
       <c r="N19" s="15">
-        <v>-10.909090909090</v>
+        <v>-7.262569832402</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G20" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H20" s="15">
-        <v>-32.352941176470</v>
+        <v>-9.375</v>
       </c>
       <c r="I20" s="14">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J20" s="14">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.658536585365</v>
+        <v>1.111111111111</v>
       </c>
       <c r="L20" s="15">
-        <v>-32.478632478632</v>
+        <v>-28.90625</v>
       </c>
       <c r="M20" s="15">
-        <v>54.901960784313</v>
+        <v>68.518518518518</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.313609467455</v>
+        <v>-87.635869565217</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D21" s="17">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.727272727272</v>
+        <v>-16.176470588235</v>
       </c>
       <c r="F21" s="17">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="G21" s="17">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.512195121951</v>
+        <v>-13.944223107569</v>
       </c>
       <c r="I21" s="17">
-        <v>583</v>
+        <v>647</v>
       </c>
       <c r="J21" s="17">
-        <v>630</v>
+        <v>698</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.460317460317</v>
+        <v>-7.306590257879</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.383916990920</v>
+        <v>-23.792697290930</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.851851851851</v>
+        <v>-1.522070015220</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.757009345794</v>
+        <v>-72.619551417689</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L22" s="15">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="M22" s="15">
-        <v>-23.076923076923</v>
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F23" s="14">
+        <v>19</v>
+      </c>
+      <c r="G23" s="14">
+        <v>19</v>
+      </c>
+      <c r="H23" s="15">
         <v>0</v>
       </c>
-      <c r="F23" s="14">
-        <v>20</v>
-      </c>
-      <c r="G23" s="14">
-        <v>25</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-20</v>
-      </c>
       <c r="I23" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J23" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.779661016949</v>
+        <v>-9.230769230769</v>
       </c>
       <c r="L23" s="15">
-        <v>3.773584905660</v>
+        <v>-3.278688524590</v>
       </c>
       <c r="M23" s="15">
-        <v>66.666666666666</v>
+        <v>63.888888888888</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D24" s="14">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E24" s="15">
-        <v>35.714285714285</v>
+        <v>-28.813559322033</v>
       </c>
       <c r="F24" s="14">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G24" s="14">
         <v>190</v>
       </c>
       <c r="H24" s="15">
-        <v>9.473684210526</v>
+        <v>5.789473684210</v>
       </c>
       <c r="I24" s="14">
-        <v>513</v>
+        <v>553</v>
       </c>
       <c r="J24" s="14">
-        <v>549</v>
+        <v>608</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.557377049180</v>
+        <v>-9.046052631578</v>
       </c>
       <c r="L24" s="15">
-        <v>1.785714285714</v>
+        <v>2.979515828677</v>
       </c>
       <c r="M24" s="15">
-        <v>54.054054054054</v>
+        <v>51.092896174863</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
         <v>21</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="F25" s="14">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G25" s="14">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H25" s="15">
-        <v>-20.512820512820</v>
+        <v>-18.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="J25" s="14">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.545454545454</v>
+        <v>-30.705394190871</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.5</v>
+        <v>-22.685185185185</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E26" s="15">
-        <v>4</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="F26" s="14">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G26" s="14">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.389380530973</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I26" s="14">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="J26" s="14">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="K26" s="15">
-        <v>1.013513513513</v>
+        <v>0.307692307692</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.142857142857</v>
+        <v>-5.232558139534</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.970189701897</v>
+        <v>-20.681265206812</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>3</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-66.666666666666</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="I27" s="14">
         <v>24</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H28" s="15">
-        <v>-14.285714285714</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J28" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K28" s="15">
-        <v>7.692307692307</v>
+        <v>3.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>34.782608695652</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-50</v>
       </c>
       <c r="F29" s="14">
-        <v>5</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G29" s="14">
+        <v>2</v>
+      </c>
+      <c r="H29" s="15">
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-15.384615384615</v>
+        <v>-20</v>
       </c>
       <c r="M29" s="15">
-        <v>-26.666666666666</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.585365853658</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>5</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>300</v>
       </c>
       <c r="I30" s="14">
+        <v>10</v>
+      </c>
+      <c r="J30" s="14">
         <v>9</v>
       </c>
-      <c r="J30" s="14">
-        <v>8</v>
-      </c>
       <c r="K30" s="15">
-        <v>12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L30" s="15">
-        <v>-25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M30" s="15">
-        <v>-30.769230769230</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.461538461538</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="J33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L33" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -199,34 +199,34 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,55 +851,55 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="C14" s="14">
+        <v>2</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>100</v>
       </c>
       <c r="F14" s="14">
+        <v>3</v>
+      </c>
+      <c r="G14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="H14" s="15">
+        <v>200</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="L14" s="15">
         <v>0</v>
       </c>
-      <c r="L14" s="15">
+      <c r="M14" s="15">
         <v>-50</v>
       </c>
-      <c r="M14" s="15">
-        <v>-66.666666666666</v>
-      </c>
       <c r="N14" s="15">
-        <v>-92.592592592592</v>
+        <v>-87.096774193548</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
         <v>21</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -914,306 +914,306 @@
         <v>19</v>
       </c>
       <c r="J15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" s="15">
+        <v>18.75</v>
+      </c>
+      <c r="L15" s="15">
         <v>26.666666666666</v>
-      </c>
-      <c r="L15" s="15">
-        <v>35.714285714285</v>
       </c>
       <c r="M15" s="15">
         <v>11.764705882352</v>
       </c>
       <c r="N15" s="15">
-        <v>-13.636363636363</v>
+        <v>-17.391304347826</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>13</v>
       </c>
       <c r="E16" s="15">
-        <v>-46.153846153846</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="F16" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
         <v>46</v>
       </c>
       <c r="H16" s="15">
-        <v>-43.478260869565</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="I16" s="14">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J16" s="14">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="K16" s="15">
-        <v>-17.525773195876</v>
+        <v>-24.545454545454</v>
       </c>
       <c r="L16" s="15">
-        <v>-48.717948717948</v>
+        <v>-51.744186046511</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.945945945945</v>
+        <v>-49.696969696969</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.095238095238</v>
+        <v>-88.645690834473</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="14">
+        <v>26</v>
+      </c>
+      <c r="D17" s="14">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>23</v>
-      </c>
-      <c r="D17" s="14">
-        <v>22</v>
-      </c>
       <c r="E17" s="15">
-        <v>4.545454545454</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G17" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H17" s="15">
-        <v>16.216216216216</v>
+        <v>6.024096385542</v>
       </c>
       <c r="I17" s="14">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="J17" s="14">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="K17" s="15">
-        <v>7.203389830508</v>
+        <v>8.076923076923</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.937984496124</v>
+        <v>-0.354609929078</v>
       </c>
       <c r="M17" s="15">
-        <v>44.571428571428</v>
+        <v>51.075268817204</v>
       </c>
       <c r="N17" s="15">
-        <v>-21.183800623053</v>
+        <v>-16.863905325443</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-68.75</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.714285714285</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="L18" s="15">
-        <v>-40</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.356435643564</v>
+        <v>-64.485981308411</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.133004926108</v>
+        <v>-91.460674157303</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15">
-        <v>-36.363636363636</v>
+        <v>-10</v>
       </c>
       <c r="F19" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.189873417721</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I19" s="14">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J19" s="14">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.821782178217</v>
+        <v>-17.567567567567</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.510917030567</v>
+        <v>-26.506024096385</v>
       </c>
       <c r="M19" s="15">
-        <v>6.410256410256</v>
+        <v>10.240963855421</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.262569832402</v>
+        <v>-6.632653061224</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G20" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>-9.375</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="J20" s="14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K20" s="15">
-        <v>1.111111111111</v>
+        <v>6.315789473684</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.90625</v>
+        <v>-27.338129496402</v>
       </c>
       <c r="M20" s="15">
-        <v>68.518518518518</v>
+        <v>71.186440677966</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.635869565217</v>
+        <v>-87.117346938775</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D21" s="17">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.176470588235</v>
+        <v>-7.575757575757</v>
       </c>
       <c r="F21" s="17">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G21" s="17">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.944223107569</v>
+        <v>-15</v>
       </c>
       <c r="I21" s="17">
-        <v>647</v>
+        <v>709</v>
       </c>
       <c r="J21" s="17">
-        <v>698</v>
+        <v>764</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.306590257879</v>
+        <v>-7.198952879581</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.792697290930</v>
+        <v>-23.516720604099</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.522070015220</v>
+        <v>0.141242937853</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.619551417689</v>
+        <v>-72.174254317111</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>100</v>
+      <c r="D22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F22" s="14">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
         <v>3</v>
       </c>
-      <c r="G22" s="14">
-        <v>4</v>
-      </c>
       <c r="H22" s="15">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>9.090909090909</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L22" s="15">
-        <v>140</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-20</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I23" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J23" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.230769230769</v>
+        <v>-12.328767123287</v>
       </c>
       <c r="L23" s="15">
-        <v>-3.278688524590</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>63.888888888888</v>
+        <v>68.421052631578</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D24" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E24" s="15">
-        <v>-28.813559322033</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="F24" s="14">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G24" s="14">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="H24" s="15">
-        <v>5.789473684210</v>
+        <v>-1.960784313725</v>
       </c>
       <c r="I24" s="14">
-        <v>553</v>
+        <v>603</v>
       </c>
       <c r="J24" s="14">
-        <v>608</v>
+        <v>670</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.046052631578</v>
+        <v>-10</v>
       </c>
       <c r="L24" s="15">
-        <v>2.979515828677</v>
+        <v>3.253424657534</v>
       </c>
       <c r="M24" s="15">
-        <v>51.092896174863</v>
+        <v>53.826530612244</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-47.619047619047</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F25" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G25" s="14">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H25" s="15">
-        <v>-18.666666666666</v>
+        <v>-12.162162162162</v>
       </c>
       <c r="I25" s="14">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J25" s="14">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="K25" s="15">
-        <v>-30.705394190871</v>
+        <v>-28.682170542635</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.685185185185</v>
+        <v>-22.689075630252</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>36</v>
+      </c>
+      <c r="D26" s="14">
         <v>27</v>
       </c>
-      <c r="D26" s="14">
-        <v>29</v>
-      </c>
       <c r="E26" s="15">
-        <v>-6.896551724137</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G26" s="14">
         <v>116</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.896551724137</v>
+        <v>2.586206896551</v>
       </c>
       <c r="I26" s="14">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="J26" s="14">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="K26" s="15">
-        <v>0.307692307692</v>
+        <v>3.409090909090</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.232558139534</v>
+        <v>-1.886792452830</v>
       </c>
       <c r="M26" s="15">
-        <v>-20.681265206812</v>
+        <v>-18.202247191011</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>-20</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I27" s="14">
         <v>24</v>
       </c>
       <c r="J27" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K27" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-4</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1429,37 +1429,37 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
         <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="15">
-        <v>-17.647058823529</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I28" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J28" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K28" s="15">
-        <v>3.333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="L28" s="15">
-        <v>34.782608695652</v>
+        <v>25.925925925925</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I29" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J29" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K29" s="15">
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-29.411764705882</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.666666666666</v>
+        <v>-82.978723404255</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>300</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J30" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K30" s="15">
-        <v>11.111111111111</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L30" s="15">
-        <v>-28.571428571428</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.235294117647</v>
+        <v>-85.227272727272</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,25 +1549,25 @@
         <v>38</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G31" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="13" t="s">
         <v>21</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
@@ -1579,10 +1579,10 @@
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,16 +1608,16 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+        <v>21</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
@@ -1635,13 +1635,13 @@
         <v>-75</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>133</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>3452</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>1789</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>2433</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>1286</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>3071</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>12273</v>

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -199,12 +199,15 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Robbery</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -852,13 +852,13 @@
         <v>19</v>
       </c>
       <c r="C14" s="14">
-        <v>2</v>
-      </c>
-      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="E14" s="15">
-        <v>100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>3</v>
@@ -870,45 +870,45 @@
         <v>200</v>
       </c>
       <c r="I14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N14" s="15">
-        <v>-87.096774193548</v>
+        <v>-86.111111111111</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
-      </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>19</v>
@@ -920,300 +920,300 @@
         <v>18.75</v>
       </c>
       <c r="L15" s="15">
-        <v>26.666666666666</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M15" s="15">
-        <v>11.764705882352</v>
+        <v>5.555555555555</v>
       </c>
       <c r="N15" s="15">
-        <v>-17.391304347826</v>
+        <v>-20.833333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-76.923076923076</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H16" s="15">
-        <v>-52.173913043478</v>
+        <v>-46.511627906976</v>
       </c>
       <c r="I16" s="14">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J16" s="14">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.545454545454</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="L16" s="15">
-        <v>-51.744186046511</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.696969696969</v>
+        <v>-49.720670391061</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.645690834473</v>
+        <v>-88.505747126436</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D17" s="14">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>8.333333333333</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F17" s="14">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G17" s="14">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H17" s="15">
-        <v>6.024096385542</v>
+        <v>13.924050632911</v>
       </c>
       <c r="I17" s="14">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="J17" s="14">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="K17" s="15">
-        <v>8.076923076923</v>
+        <v>10.256410256410</v>
       </c>
       <c r="L17" s="15">
-        <v>-0.354609929078</v>
+        <v>1.006711409395</v>
       </c>
       <c r="M17" s="15">
-        <v>51.075268817204</v>
+        <v>46.829268292682</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.863905325443</v>
+        <v>-20.159151193634</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-57.142857142857</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J18" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K18" s="15">
-        <v>-34.482758620689</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.424242424242</v>
+        <v>-45.205479452054</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.485981308411</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.460674157303</v>
+        <v>-91.649269311064</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
         <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E19" s="15">
-        <v>-10</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F19" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G19" s="14">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.047619047619</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="J19" s="14">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.567567567567</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.506024096385</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="M19" s="15">
-        <v>10.240963855421</v>
+        <v>13.407821229050</v>
       </c>
       <c r="N19" s="15">
-        <v>-6.632653061224</v>
+        <v>-4.694835680751</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
         <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F20" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G20" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>14.285714285714</v>
+        <v>40.740740740740</v>
       </c>
       <c r="I20" s="14">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J20" s="14">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="K20" s="15">
-        <v>6.315789473684</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.338129496402</v>
+        <v>-26.797385620915</v>
       </c>
       <c r="M20" s="15">
-        <v>71.186440677966</v>
+        <v>69.696969696969</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.117346938775</v>
+        <v>-86.424242424242</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D21" s="17">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.575757575757</v>
+        <v>1.818181818181</v>
       </c>
       <c r="F21" s="17">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G21" s="17">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H21" s="18">
-        <v>-15</v>
+        <v>-8.627450980392</v>
       </c>
       <c r="I21" s="17">
-        <v>709</v>
+        <v>770</v>
       </c>
       <c r="J21" s="17">
-        <v>764</v>
+        <v>819</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.198952879581</v>
+        <v>-5.982905982905</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.516720604099</v>
+        <v>-23</v>
       </c>
       <c r="M21" s="18">
-        <v>0.141242937853</v>
+        <v>-0.129701686121</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.174254317111</v>
+        <v>-71.867007672634</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>400</v>
       </c>
       <c r="I22" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L22" s="15">
-        <v>133.333333333333</v>
+        <v>150</v>
       </c>
       <c r="M22" s="15">
-        <v>-17.647058823529</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G23" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H23" s="15">
-        <v>-10</v>
+        <v>-36</v>
       </c>
       <c r="I23" s="14">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J23" s="14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K23" s="15">
-        <v>-12.328767123287</v>
+        <v>-15.189873417721</v>
       </c>
       <c r="L23" s="15">
-        <v>-8.571428571428</v>
+        <v>-11.842105263157</v>
       </c>
       <c r="M23" s="15">
-        <v>68.421052631578</v>
+        <v>63.414634146341</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D24" s="14">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="E24" s="15">
-        <v>-22.580645161290</v>
+        <v>70</v>
       </c>
       <c r="F24" s="14">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="G24" s="14">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.960784313725</v>
+        <v>6.403940886699</v>
       </c>
       <c r="I24" s="14">
-        <v>603</v>
+        <v>669</v>
       </c>
       <c r="J24" s="14">
-        <v>670</v>
+        <v>710</v>
       </c>
       <c r="K24" s="15">
-        <v>-10</v>
+        <v>-5.774647887323</v>
       </c>
       <c r="L24" s="15">
-        <v>3.253424657534</v>
+        <v>9.135399673735</v>
       </c>
       <c r="M24" s="15">
-        <v>53.826530612244</v>
+        <v>57.411764705882</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-17.647058823529</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G25" s="14">
         <v>74</v>
       </c>
       <c r="H25" s="15">
-        <v>-12.162162162162</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="I25" s="14">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="J25" s="14">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.682170542635</v>
+        <v>-24.542124542124</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.689075630252</v>
+        <v>-16.935483870967</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D26" s="14">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="F26" s="14">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G26" s="14">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H26" s="15">
-        <v>2.586206896551</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="J26" s="14">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="K26" s="15">
-        <v>3.409090909090</v>
+        <v>0.771208226221</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.886792452830</v>
+        <v>-0.759493670886</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.202247191011</v>
+        <v>-19.507186858316</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="14">
-        <v>3</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J27" s="14">
         <v>24</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-11.111111111111</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H28" s="15">
-        <v>-22.222222222222</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K28" s="15">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>25.925925925925</v>
+        <v>24.137931034482</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>4</v>
-      </c>
-      <c r="D29" s="14">
-        <v>4</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G29" s="14">
         <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I29" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" s="14">
         <v>16</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="L29" s="15">
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-11.111111111111</v>
+        <v>-32</v>
       </c>
       <c r="N29" s="15">
-        <v>-82.978723404255</v>
+        <v>-84.684684684684</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>3</v>
-      </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J30" s="14">
         <v>11</v>
       </c>
       <c r="K30" s="15">
-        <v>18.181818181818</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L30" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="M30" s="15">
-        <v>-18.75</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.227272727272</v>
+        <v>-86.274509803921</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,25 +1549,25 @@
         <v>38</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
@@ -1579,10 +1579,10 @@
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,16 +1608,16 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>133</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>3452</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>1789</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>2433</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>1286</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>3071</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>12273</v>

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -882,10 +882,10 @@
         <v>25</v>
       </c>
       <c r="M14" s="15">
-        <v>-44.444444444444</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N14" s="15">
-        <v>-86.111111111111</v>
+        <v>-86.842105263157</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,38 +895,38 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>19</v>
       </c>
       <c r="J15" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K15" s="15">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>11.764705882352</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>5.555555555555</v>
+        <v>-5</v>
       </c>
       <c r="N15" s="15">
-        <v>-20.833333333333</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>16.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H16" s="15">
-        <v>-46.511627906976</v>
+        <v>-45.238095238095</v>
       </c>
       <c r="I16" s="14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J16" s="14">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="K16" s="15">
-        <v>-22.413793103448</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="L16" s="15">
-        <v>-52.380952380952</v>
+        <v>-51.269035532994</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.720670391061</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.505747126436</v>
+        <v>-88.461538461538</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E17" s="15">
-        <v>38.461538461538</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F17" s="14">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G17" s="14">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H17" s="15">
-        <v>13.924050632911</v>
+        <v>12.345679012345</v>
       </c>
       <c r="I17" s="14">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="J17" s="14">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="K17" s="15">
-        <v>10.256410256410</v>
+        <v>9.491525423728</v>
       </c>
       <c r="L17" s="15">
-        <v>1.006711409395</v>
+        <v>3.858520900321</v>
       </c>
       <c r="M17" s="15">
-        <v>46.829268292682</v>
+        <v>48.165137614678</v>
       </c>
       <c r="N17" s="15">
-        <v>-20.159151193634</v>
+        <v>-20.638820638820</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-41.666666666666</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.483870967741</v>
+        <v>-38.805970149253</v>
       </c>
       <c r="L18" s="15">
-        <v>-45.205479452054</v>
+        <v>-48.75</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.217391304347</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.649269311064</v>
+        <v>-92.084942084942</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-21.739130434782</v>
+        <v>111.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G19" s="14">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="H19" s="15">
-        <v>-21.111111111111</v>
+        <v>-1.351351351351</v>
       </c>
       <c r="I19" s="14">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="J19" s="14">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.142857142857</v>
+        <v>-12.598425196850</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.684210526315</v>
+        <v>-21.554770318021</v>
       </c>
       <c r="M19" s="15">
-        <v>13.407821229050</v>
+        <v>15.625</v>
       </c>
       <c r="N19" s="15">
-        <v>-4.694835680751</v>
+        <v>-4.310344827586</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E20" s="15">
-        <v>11.111111111111</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="F20" s="14">
         <v>38</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H20" s="15">
-        <v>40.740740740740</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I20" s="14">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J20" s="14">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="K20" s="15">
-        <v>7.692307692307</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.797385620915</v>
+        <v>-30.120481927710</v>
       </c>
       <c r="M20" s="15">
-        <v>69.696969696969</v>
+        <v>61.111111111111</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.424242424242</v>
+        <v>-86.951631046119</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E21" s="18">
-        <v>1.818181818181</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F21" s="17">
         <v>233</v>
       </c>
       <c r="G21" s="17">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.627450980392</v>
+        <v>-7.539682539682</v>
       </c>
       <c r="I21" s="17">
-        <v>770</v>
+        <v>822</v>
       </c>
       <c r="J21" s="17">
-        <v>819</v>
+        <v>882</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.982905982905</v>
+        <v>-6.802721088435</v>
       </c>
       <c r="L21" s="18">
-        <v>-23</v>
+        <v>-22.452830188679</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.129701686121</v>
+        <v>-0.724637681159</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.867007672634</v>
+        <v>-72.050323019381</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="I22" s="14">
         <v>15</v>
       </c>
       <c r="J22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>36.363636363636</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>150</v>
+        <v>87.5</v>
       </c>
       <c r="M22" s="15">
         <v>-21.052631578947</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F23" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H23" s="15">
-        <v>-36</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I23" s="14">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J23" s="14">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K23" s="15">
-        <v>-15.189873417721</v>
+        <v>-19.767441860465</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.842105263157</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="M23" s="15">
-        <v>63.414634146341</v>
+        <v>56.818181818181</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D24" s="14">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E24" s="15">
-        <v>70</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="14">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="G24" s="14">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H24" s="15">
-        <v>6.403940886699</v>
+        <v>-7.981220657277</v>
       </c>
       <c r="I24" s="14">
-        <v>669</v>
+        <v>707</v>
       </c>
       <c r="J24" s="14">
-        <v>710</v>
+        <v>762</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.774647887323</v>
+        <v>-7.217847769028</v>
       </c>
       <c r="L24" s="15">
-        <v>9.135399673735</v>
+        <v>6.959152798789</v>
       </c>
       <c r="M24" s="15">
-        <v>57.411764705882</v>
+        <v>57.461024498886</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
         <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G25" s="14">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H25" s="15">
-        <v>-2.702702702702</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="I25" s="14">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="J25" s="14">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.542124542124</v>
+        <v>-22.916666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.935483870967</v>
+        <v>-16.541353383458</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>32</v>
+      </c>
+      <c r="D26" s="14">
+        <v>25</v>
+      </c>
+      <c r="E26" s="15">
         <v>28</v>
       </c>
-      <c r="D26" s="14">
-        <v>37</v>
-      </c>
-      <c r="E26" s="15">
-        <v>-24.324324324324</v>
-      </c>
       <c r="F26" s="14">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G26" s="14">
         <v>118</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>3.389830508474</v>
       </c>
       <c r="I26" s="14">
-        <v>392</v>
+        <v>423</v>
       </c>
       <c r="J26" s="14">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="K26" s="15">
-        <v>0.771208226221</v>
+        <v>2.173913043478</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.759493670886</v>
+        <v>1.927710843373</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.507186858316</v>
+        <v>-17.864077669902</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1403,16 +1403,16 @@
         <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J27" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K27" s="15">
-        <v>4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-13.793103448275</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H28" s="15">
-        <v>-6.666666666666</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J28" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>2.702702702702</v>
       </c>
       <c r="L28" s="15">
-        <v>24.137931034482</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1485,22 +1485,22 @@
         <v>16.666666666666</v>
       </c>
       <c r="I29" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J29" s="14">
         <v>16</v>
       </c>
       <c r="K29" s="15">
-        <v>6.25</v>
+        <v>12.5</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M29" s="15">
-        <v>-32</v>
+        <v>-28</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.684684684684</v>
+        <v>-84.482758620689</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1526,22 +1526,22 @@
         <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J30" s="14">
         <v>11</v>
       </c>
       <c r="K30" s="15">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L30" s="15">
-        <v>-12.5</v>
+        <v>-6.25</v>
       </c>
       <c r="M30" s="15">
-        <v>-26.315789473684</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.274509803921</v>
+        <v>-85.981308411215</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,31 +861,31 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L14" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M14" s="15">
-        <v>-54.545454545454</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N14" s="15">
-        <v>-86.842105263157</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -914,19 +914,19 @@
         <v>19</v>
       </c>
       <c r="J15" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M15" s="15">
-        <v>-5</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="N15" s="15">
-        <v>-24</v>
+        <v>-38.709677419354</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
         <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-45.238095238095</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="I16" s="14">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="J16" s="14">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.809523809523</v>
+        <v>-20.769230769230</v>
       </c>
       <c r="L16" s="15">
-        <v>-51.269035532994</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-50.717703349282</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.461538461538</v>
+        <v>-88.426966292134</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="14">
         <v>22</v>
       </c>
       <c r="E17" s="15">
-        <v>-9.090909090909</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="F17" s="14">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G17" s="14">
         <v>81</v>
       </c>
       <c r="H17" s="15">
-        <v>12.345679012345</v>
+        <v>6.172839506172</v>
       </c>
       <c r="I17" s="14">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="J17" s="14">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="K17" s="15">
-        <v>9.491525423728</v>
+        <v>8.201892744479</v>
       </c>
       <c r="L17" s="15">
-        <v>3.858520900321</v>
+        <v>3.003003003003</v>
       </c>
       <c r="M17" s="15">
-        <v>48.165137614678</v>
+        <v>45.957446808510</v>
       </c>
       <c r="N17" s="15">
-        <v>-20.638820638820</v>
+        <v>-21.330275229357</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-80</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-64.285714285714</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J18" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.805970149253</v>
+        <v>-38.028169014084</v>
       </c>
       <c r="L18" s="15">
-        <v>-48.75</v>
+        <v>-48.235294117647</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.666666666666</v>
+        <v>-66.412213740458</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.084942084942</v>
+        <v>-92.156862745098</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>111.111111111111</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F19" s="14">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G19" s="14">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>-1.351351351351</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I19" s="14">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="J19" s="14">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.598425196850</v>
+        <v>-11.985018726591</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.554770318021</v>
+        <v>-20.875420875420</v>
       </c>
       <c r="M19" s="15">
-        <v>15.625</v>
+        <v>13.526570048309</v>
       </c>
       <c r="N19" s="15">
-        <v>-4.310344827586</v>
+        <v>-7.480314960629</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-78.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G20" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" s="15">
-        <v>5.555555555555</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="I20" s="14">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="J20" s="14">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K20" s="15">
-        <v>-1.694915254237</v>
+        <v>-3.149606299212</v>
       </c>
       <c r="L20" s="15">
-        <v>-30.120481927710</v>
+        <v>-30.508474576271</v>
       </c>
       <c r="M20" s="15">
-        <v>61.111111111111</v>
+        <v>53.75</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.951631046119</v>
+        <v>-86.970338983050</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.809523809523</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="F21" s="17">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="G21" s="17">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.539682539682</v>
+        <v>-6.722689075630</v>
       </c>
       <c r="I21" s="17">
-        <v>822</v>
+        <v>873</v>
       </c>
       <c r="J21" s="17">
-        <v>882</v>
+        <v>936</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.802721088435</v>
+        <v>-6.730769230769</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.452830188679</v>
+        <v>-22.261798753339</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.724637681159</v>
+        <v>-2.348993288590</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.050323019381</v>
+        <v>-72.338403041825</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>5</v>
-      </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
       <c r="H22" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
         <v>15</v>
@@ -1210,7 +1210,7 @@
         <v>87.5</v>
       </c>
       <c r="M22" s="15">
-        <v>-21.052631578947</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-71.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H23" s="15">
-        <v>-55.555555555555</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I23" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J23" s="14">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K23" s="15">
-        <v>-19.767441860465</v>
+        <v>-19.780219780219</v>
       </c>
       <c r="L23" s="15">
-        <v>-14.814814814814</v>
+        <v>-15.116279069767</v>
       </c>
       <c r="M23" s="15">
-        <v>56.818181818181</v>
+        <v>46</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D24" s="14">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>15.555555555555</v>
       </c>
       <c r="F24" s="14">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="G24" s="14">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.981220657277</v>
+        <v>4.020100502512</v>
       </c>
       <c r="I24" s="14">
-        <v>707</v>
+        <v>761</v>
       </c>
       <c r="J24" s="14">
-        <v>762</v>
+        <v>807</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.217847769028</v>
+        <v>-5.700123915737</v>
       </c>
       <c r="L24" s="15">
-        <v>6.959152798789</v>
+        <v>7.637906647807</v>
       </c>
       <c r="M24" s="15">
-        <v>57.461024498886</v>
+        <v>58.541666666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>6.666666666666</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="F25" s="14">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G25" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H25" s="15">
-        <v>-2.941176470588</v>
+        <v>5.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="J25" s="14">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="K25" s="15">
-        <v>-22.916666666666</v>
+        <v>-21.543408360128</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.541353383458</v>
+        <v>-12.857142857142</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E26" s="15">
-        <v>28</v>
+        <v>-46.341463414634</v>
       </c>
       <c r="F26" s="14">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G26" s="14">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H26" s="15">
-        <v>3.389830508474</v>
+        <v>-10.769230769230</v>
       </c>
       <c r="I26" s="14">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="J26" s="14">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="K26" s="15">
-        <v>2.173913043478</v>
+        <v>-2.417582417582</v>
       </c>
       <c r="L26" s="15">
-        <v>1.927710843373</v>
+        <v>-0.448430493273</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.864077669902</v>
+        <v>-20.572450805008</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I27" s="14">
         <v>27</v>
       </c>
       <c r="J27" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L27" s="15">
-        <v>-12.903225806451</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
         <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>-8.333333333333</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I28" s="14">
+        <v>41</v>
+      </c>
+      <c r="J28" s="14">
         <v>38</v>
       </c>
-      <c r="J28" s="14">
-        <v>37</v>
-      </c>
       <c r="K28" s="15">
-        <v>2.702702702702</v>
+        <v>7.894736842105</v>
       </c>
       <c r="L28" s="15">
-        <v>11.764705882352</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,28 +1479,28 @@
         <v>7</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>16.666666666666</v>
+        <v>75</v>
       </c>
       <c r="I29" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J29" s="14">
         <v>16</v>
       </c>
       <c r="K29" s="15">
-        <v>12.5</v>
+        <v>18.75</v>
       </c>
       <c r="L29" s="15">
-        <v>5.882352941176</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M29" s="15">
-        <v>-28</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.482758620689</v>
+        <v>-84.552845528455</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,28 +1520,28 @@
         <v>6</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I30" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J30" s="14">
         <v>11</v>
       </c>
       <c r="K30" s="15">
-        <v>36.363636363636</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L30" s="15">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-21.052631578947</v>
+        <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.981308411215</v>
+        <v>-85.964912280701</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1635,7 +1635,7 @@
         <v>-75</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,13 +861,13 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>4</v>
-      </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>6</v>
@@ -885,48 +885,48 @@
         <v>-45.454545454545</v>
       </c>
       <c r="N14" s="15">
-        <v>-85</v>
+        <v>-85.365853658536</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
+        <v>-50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-85.714285714285</v>
+      </c>
+      <c r="I15" s="14">
         <v>20</v>
       </c>
-      <c r="G15" s="14">
-        <v>6</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="14">
-        <v>19</v>
-      </c>
       <c r="J15" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K15" s="15">
-        <v>-9.523809523809</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L15" s="15">
-        <v>-9.523809523809</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M15" s="15">
-        <v>-9.523809523809</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="N15" s="15">
-        <v>-38.709677419354</v>
+        <v>-44.444444444444</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H16" s="15">
-        <v>-30.303030303030</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I16" s="14">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="J16" s="14">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.769230769230</v>
+        <v>-19.424460431654</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-49.549549549549</v>
       </c>
       <c r="M16" s="15">
-        <v>-50.717703349282</v>
+        <v>-51.304347826087</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.426966292134</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E17" s="15">
-        <v>-13.636363636363</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="14">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G17" s="14">
         <v>81</v>
       </c>
       <c r="H17" s="15">
-        <v>6.172839506172</v>
+        <v>-9.876543209876</v>
       </c>
       <c r="I17" s="14">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="J17" s="14">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="K17" s="15">
-        <v>8.201892744479</v>
+        <v>4.985337243401</v>
       </c>
       <c r="L17" s="15">
-        <v>3.003003003003</v>
+        <v>0.280112044817</v>
       </c>
       <c r="M17" s="15">
-        <v>45.957446808510</v>
+        <v>44.939271255060</v>
       </c>
       <c r="N17" s="15">
-        <v>-21.330275229357</v>
+        <v>-23.175965665236</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-46.666666666666</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I18" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J18" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.028169014084</v>
+        <v>-34.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-48.235294117647</v>
+        <v>-46.739130434782</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.412213740458</v>
+        <v>-65.972222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.156862745098</v>
+        <v>-91.708967851099</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.692307692307</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G19" s="14">
         <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>7.692307692307</v>
+        <v>6.153846153846</v>
       </c>
       <c r="I19" s="14">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="J19" s="14">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.985018726591</v>
+        <v>-11.498257839721</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.875420875420</v>
+        <v>-19.108280254777</v>
       </c>
       <c r="M19" s="15">
-        <v>13.526570048309</v>
+        <v>15.454545454545</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.480314960629</v>
+        <v>-6.617647058823</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F20" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G20" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.216216216216</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="I20" s="14">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="J20" s="14">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.149606299212</v>
+        <v>-5.797101449275</v>
       </c>
       <c r="L20" s="15">
-        <v>-30.508474576271</v>
+        <v>-30.851063829787</v>
       </c>
       <c r="M20" s="15">
-        <v>53.75</v>
+        <v>58.536585365853</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.970338983050</v>
+        <v>-86.721144024514</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.962962962963</v>
+        <v>-24.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="G21" s="17">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.722689075630</v>
+        <v>-12.396694214876</v>
       </c>
       <c r="I21" s="17">
-        <v>873</v>
+        <v>929</v>
       </c>
       <c r="J21" s="17">
-        <v>936</v>
+        <v>1006</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.730769230769</v>
+        <v>-7.654075546719</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.261798753339</v>
+        <v>-22.776392352452</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.348993288590</v>
+        <v>-2.722513089005</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.338403041825</v>
+        <v>-72.160623314354</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>15</v>
@@ -1210,7 +1210,7 @@
         <v>87.5</v>
       </c>
       <c r="M22" s="15">
-        <v>-25</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F23" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
         <v>26</v>
       </c>
       <c r="H23" s="15">
-        <v>-46.153846153846</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I23" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J23" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K23" s="15">
-        <v>-19.780219780219</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L23" s="15">
-        <v>-15.116279069767</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M23" s="15">
-        <v>46</v>
+        <v>38.888888888888</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D24" s="14">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="E24" s="15">
-        <v>15.555555555555</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="F24" s="14">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="G24" s="14">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="H24" s="15">
-        <v>4.020100502512</v>
+        <v>5.687203791469</v>
       </c>
       <c r="I24" s="14">
-        <v>761</v>
+        <v>823</v>
       </c>
       <c r="J24" s="14">
-        <v>807</v>
+        <v>881</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.700123915737</v>
+        <v>-6.583427922814</v>
       </c>
       <c r="L24" s="15">
-        <v>7.637906647807</v>
+        <v>8.432147562582</v>
       </c>
       <c r="M24" s="15">
-        <v>58.541666666666</v>
+        <v>63.944223107569</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E25" s="15">
-        <v>-17.391304347826</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F25" s="14">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G25" s="14">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="H25" s="15">
-        <v>5.714285714285</v>
+        <v>-15.116279069767</v>
       </c>
       <c r="I25" s="14">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="J25" s="14">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="K25" s="15">
-        <v>-21.543408360128</v>
+        <v>-24.709302325581</v>
       </c>
       <c r="L25" s="15">
-        <v>-12.857142857142</v>
+        <v>-14.238410596026</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D26" s="14">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E26" s="15">
-        <v>-46.341463414634</v>
+        <v>9.677419354838</v>
       </c>
       <c r="F26" s="14">
         <v>116</v>
       </c>
       <c r="G26" s="14">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.769230769230</v>
+        <v>-13.432835820895</v>
       </c>
       <c r="I26" s="14">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="J26" s="14">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.417582417582</v>
+        <v>-1.440329218107</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.448430493273</v>
+        <v>2.132196162046</v>
       </c>
       <c r="M26" s="15">
-        <v>-20.572450805008</v>
+        <v>-18.950930626057</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="14">
         <v>3</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
-      </c>
       <c r="G27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-77.777777777777</v>
+        <v>-62.5</v>
       </c>
       <c r="I27" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J27" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K27" s="15">
-        <v>-10</v>
+        <v>-12.5</v>
       </c>
       <c r="L27" s="15">
-        <v>-18.181818181818</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>-40</v>
       </c>
       <c r="F28" s="14">
         <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H28" s="15">
-        <v>22.222222222222</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J28" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K28" s="15">
-        <v>7.894736842105</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-2.380952380952</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F29" s="14">
+        <v>4</v>
+      </c>
+      <c r="G29" s="14">
+        <v>2</v>
+      </c>
+      <c r="H29" s="15">
+        <v>100</v>
+      </c>
+      <c r="I29" s="14">
         <v>20</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="14">
-        <v>7</v>
-      </c>
-      <c r="G29" s="14">
-        <v>4</v>
-      </c>
-      <c r="H29" s="15">
-        <v>75</v>
-      </c>
-      <c r="I29" s="14">
-        <v>19</v>
-      </c>
       <c r="J29" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K29" s="15">
-        <v>18.75</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L29" s="15">
-        <v>11.764705882352</v>
+        <v>17.647058823529</v>
       </c>
       <c r="M29" s="15">
-        <v>-26.923076923076</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.552845528455</v>
+        <v>-84.375</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-50</v>
       </c>
       <c r="F30" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J30" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K30" s="15">
-        <v>45.454545454545</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="M30" s="15">
-        <v>-20</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.964912280701</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-075pct.xlsx
+++ b/data/source/weekly/cs-en-us-075pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,63 +870,63 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L14" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M14" s="15">
-        <v>-45.454545454545</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N14" s="15">
-        <v>-85.365853658536</v>
+        <v>-84.444444444444</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15" s="15">
-        <v>-85.714285714285</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K15" s="15">
-        <v>-13.043478260869</v>
+        <v>-12.5</v>
       </c>
       <c r="L15" s="15">
-        <v>-23.076923076923</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M15" s="15">
-        <v>-4.761904761904</v>
+        <v>-16</v>
       </c>
       <c r="N15" s="15">
-        <v>-44.444444444444</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G16" s="14">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H16" s="15">
-        <v>-3.448275862068</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="I16" s="14">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="J16" s="14">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K16" s="15">
-        <v>-19.424460431654</v>
+        <v>-18.300653594771</v>
       </c>
       <c r="L16" s="15">
-        <v>-49.549549549549</v>
+        <v>-47.033898305084</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.304347826087</v>
+        <v>-50.199203187251</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.235294117647</v>
+        <v>-87.599206349206</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>23</v>
+      </c>
+      <c r="D17" s="14">
         <v>15</v>
       </c>
-      <c r="D17" s="14">
-        <v>24</v>
-      </c>
       <c r="E17" s="15">
-        <v>-37.5</v>
+        <v>53.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G17" s="14">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.876543209876</v>
+        <v>-7.228915662650</v>
       </c>
       <c r="I17" s="14">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="J17" s="14">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="K17" s="15">
-        <v>4.985337243401</v>
+        <v>7.022471910112</v>
       </c>
       <c r="L17" s="15">
-        <v>0.280112044817</v>
+        <v>-0.261780104712</v>
       </c>
       <c r="M17" s="15">
-        <v>44.939271255060</v>
+        <v>47.674418604651</v>
       </c>
       <c r="N17" s="15">
-        <v>-23.175965665236</v>
+        <v>-23.340040241448</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-35.294117647058</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="I18" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K18" s="15">
-        <v>-34.666666666666</v>
+        <v>-35.802469135802</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.739130434782</v>
+        <v>-46.391752577319</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.972222222222</v>
+        <v>-66.233766233766</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.708967851099</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="F19" s="14">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G19" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H19" s="15">
-        <v>6.153846153846</v>
+        <v>10.958904109589</v>
       </c>
       <c r="I19" s="14">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="J19" s="14">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.498257839721</v>
+        <v>-9.748427672955</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.108280254777</v>
+        <v>-12.232415902140</v>
       </c>
       <c r="M19" s="15">
-        <v>15.454545454545</v>
+        <v>25.327510917030</v>
       </c>
       <c r="N19" s="15">
-        <v>-6.617647058823</v>
+        <v>-2.711864406779</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-36.363636363636</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H20" s="15">
-        <v>-34.883720930232</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="I20" s="14">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J20" s="14">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K20" s="15">
-        <v>-5.797101449275</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="L20" s="15">
-        <v>-30.851063829787</v>
+        <v>-35.406698564593</v>
       </c>
       <c r="M20" s="15">
-        <v>58.536585365853</v>
+        <v>56.976744186046</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.721144024514</v>
+        <v>-86.790606653620</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D21" s="17">
         <v>70</v>
       </c>
       <c r="E21" s="18">
-        <v>-24.285714285714</v>
+        <v>1.428571428571</v>
       </c>
       <c r="F21" s="17">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="G21" s="17">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.396694214876</v>
+        <v>-10.894941634241</v>
       </c>
       <c r="I21" s="17">
-        <v>929</v>
+        <v>1008</v>
       </c>
       <c r="J21" s="17">
-        <v>1006</v>
+        <v>1076</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.654075546719</v>
+        <v>-6.319702602230</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.776392352452</v>
+        <v>-21.372854914196</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.722513089005</v>
+        <v>-0.591715976331</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.160623314354</v>
+        <v>-71.452846219201</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>15</v>
@@ -1207,10 +1207,10 @@
         <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>87.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-31.818181818181</v>
+        <v>-37.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H23" s="15">
-        <v>-53.846153846153</v>
+        <v>-56.25</v>
       </c>
       <c r="I23" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J23" s="14">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="K23" s="15">
-        <v>-24.242424242424</v>
+        <v>-27.927927927927</v>
       </c>
       <c r="L23" s="15">
-        <v>-21.052631578947</v>
+        <v>-20.792079207920</v>
       </c>
       <c r="M23" s="15">
-        <v>38.888888888888</v>
+        <v>31.147540983606</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D24" s="14">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.216216216216</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F24" s="14">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="G24" s="14">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="H24" s="15">
-        <v>5.687203791469</v>
+        <v>-12.393162393162</v>
       </c>
       <c r="I24" s="14">
-        <v>823</v>
+        <v>871</v>
       </c>
       <c r="J24" s="14">
-        <v>881</v>
+        <v>944</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.583427922814</v>
+        <v>-7.733050847457</v>
       </c>
       <c r="L24" s="15">
-        <v>8.432147562582</v>
+        <v>6.740196078431</v>
       </c>
       <c r="M24" s="15">
-        <v>63.944223107569</v>
+        <v>68.471953578336</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>-54.545454545454</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G25" s="14">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.116279069767</v>
+        <v>-29.473684210526</v>
       </c>
       <c r="I25" s="14">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="J25" s="14">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.709302325581</v>
+        <v>-25.815217391304</v>
       </c>
       <c r="L25" s="15">
-        <v>-14.238410596026</v>
+        <v>-15.479876160990</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D26" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>9.677419354838</v>
+        <v>12</v>
       </c>
       <c r="F26" s="14">
         <v>116</v>
       </c>
       <c r="G26" s="14">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.432835820895</v>
+        <v>-4.918032786885</v>
       </c>
       <c r="I26" s="14">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="J26" s="14">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.440329218107</v>
+        <v>-0.978473581213</v>
       </c>
       <c r="L26" s="15">
-        <v>2.132196162046</v>
+        <v>-0.978473581213</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.950930626057</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>28</v>
       </c>
       <c r="J27" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K27" s="15">
-        <v>-12.5</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="L27" s="15">
-        <v>-26.315789473684</v>
+        <v>-30</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="14">
-        <v>5</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-40</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-8.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J28" s="14">
         <v>43</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>6.976744186046</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-50</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>4</v>
@@ -1485,22 +1485,22 @@
         <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" s="14">
         <v>18</v>
       </c>
       <c r="K29" s="15">
-        <v>11.111111111111</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>17.647058823529</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-31.034482758620</v>
+        <v>-30</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.375</v>
+        <v>-84.558823529411</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-50</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>4</v>
@@ -1526,22 +1526,22 @@
         <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J30" s="14">
         <v>13</v>
       </c>
       <c r="K30" s="15">
-        <v>30.769230769230</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L30" s="15">
-        <v>6.25</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M30" s="15">
-        <v>-26.086956521739</v>
+        <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.714285714285</v>
+        <v>-85.826771653543</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
